--- a/AAII_Financials/Yearly/SFHG_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SFHG_YR_FIN.xlsx
@@ -2208,7 +2208,7 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="E59" s="3">
         <v>1200</v>
